--- a/artfynd/A 47876-2025 artfynd.xlsx
+++ b/artfynd/A 47876-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129669963</v>
       </c>
       <c r="B2" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129669857</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129669907</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129669938</v>
+        <v>129669806</v>
       </c>
       <c r="B5" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498751</v>
+        <v>498780</v>
       </c>
       <c r="R5" t="n">
-        <v>6850235</v>
+        <v>6850297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129669806</v>
+        <v>129669938</v>
       </c>
       <c r="B6" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498780</v>
+        <v>498751</v>
       </c>
       <c r="R6" t="n">
-        <v>6850297</v>
+        <v>6850235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 47876-2025 artfynd.xlsx
+++ b/artfynd/A 47876-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129669963</v>
       </c>
       <c r="B2" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129669857</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129669907</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129669806</v>
+        <v>129669938</v>
       </c>
       <c r="B5" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498780</v>
+        <v>498751</v>
       </c>
       <c r="R5" t="n">
-        <v>6850297</v>
+        <v>6850235</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129669938</v>
+        <v>129669806</v>
       </c>
       <c r="B6" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498751</v>
+        <v>498780</v>
       </c>
       <c r="R6" t="n">
-        <v>6850235</v>
+        <v>6850297</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 47876-2025 artfynd.xlsx
+++ b/artfynd/A 47876-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129669963</v>
       </c>
       <c r="B2" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129669857</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129669907</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129669938</v>
+        <v>129669806</v>
       </c>
       <c r="B5" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498751</v>
+        <v>498780</v>
       </c>
       <c r="R5" t="n">
-        <v>6850235</v>
+        <v>6850297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129669806</v>
+        <v>129669938</v>
       </c>
       <c r="B6" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498780</v>
+        <v>498751</v>
       </c>
       <c r="R6" t="n">
-        <v>6850297</v>
+        <v>6850235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 47876-2025 artfynd.xlsx
+++ b/artfynd/A 47876-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129669963</v>
       </c>
       <c r="B2" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129669857</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129669907</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129669806</v>
       </c>
       <c r="B5" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129669938</v>
       </c>
       <c r="B6" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47876-2025 artfynd.xlsx
+++ b/artfynd/A 47876-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129669907</v>
+        <v>129669806</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>92913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498744</v>
+        <v>498780</v>
       </c>
       <c r="R4" t="n">
-        <v>6850260</v>
+        <v>6850297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Med apothecier.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129669806</v>
+        <v>129669938</v>
       </c>
       <c r="B5" t="n">
         <v>92913</v>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498780</v>
+        <v>498751</v>
       </c>
       <c r="R5" t="n">
-        <v>6850297</v>
+        <v>6850235</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129669938</v>
+        <v>129669907</v>
       </c>
       <c r="B6" t="n">
-        <v>92913</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498751</v>
+        <v>498744</v>
       </c>
       <c r="R6" t="n">
-        <v>6850235</v>
+        <v>6850260</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Med apothecier.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 47876-2025 artfynd.xlsx
+++ b/artfynd/A 47876-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129669938</v>
+        <v>129669907</v>
       </c>
       <c r="B5" t="n">
-        <v>92913</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498751</v>
+        <v>498744</v>
       </c>
       <c r="R5" t="n">
-        <v>6850235</v>
+        <v>6850260</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Med apothecier.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129669907</v>
+        <v>129669938</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>92913</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498744</v>
+        <v>498751</v>
       </c>
       <c r="R6" t="n">
-        <v>6850260</v>
+        <v>6850235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Med apothecier.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 47876-2025 artfynd.xlsx
+++ b/artfynd/A 47876-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129669806</v>
+        <v>129669907</v>
       </c>
       <c r="B4" t="n">
-        <v>92913</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498780</v>
+        <v>498744</v>
       </c>
       <c r="R4" t="n">
-        <v>6850297</v>
+        <v>6850260</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Med apothecier.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129669907</v>
+        <v>129669806</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>92913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498744</v>
+        <v>498780</v>
       </c>
       <c r="R5" t="n">
-        <v>6850260</v>
+        <v>6850297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Med apothecier.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 47876-2025 artfynd.xlsx
+++ b/artfynd/A 47876-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>129669806</v>
       </c>
       <c r="B5" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129669938</v>
       </c>
       <c r="B6" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47876-2025 artfynd.xlsx
+++ b/artfynd/A 47876-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>129669806</v>
       </c>
       <c r="B5" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129669938</v>
       </c>
       <c r="B6" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47876-2025 artfynd.xlsx
+++ b/artfynd/A 47876-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129669963</v>
       </c>
       <c r="B2" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129669857</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129669907</v>
+        <v>129669806</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>92922</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498744</v>
+        <v>498780</v>
       </c>
       <c r="R4" t="n">
-        <v>6850260</v>
+        <v>6850297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Med apothecier.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129669806</v>
+        <v>129669938</v>
       </c>
       <c r="B5" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498780</v>
+        <v>498751</v>
       </c>
       <c r="R5" t="n">
-        <v>6850297</v>
+        <v>6850235</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129669938</v>
+        <v>129669907</v>
       </c>
       <c r="B6" t="n">
-        <v>92919</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498751</v>
+        <v>498744</v>
       </c>
       <c r="R6" t="n">
-        <v>6850235</v>
+        <v>6850260</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Med apothecier.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 47876-2025 artfynd.xlsx
+++ b/artfynd/A 47876-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129669963</v>
       </c>
       <c r="B2" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129669857</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129669806</v>
+        <v>129669907</v>
       </c>
       <c r="B4" t="n">
-        <v>92922</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498780</v>
+        <v>498744</v>
       </c>
       <c r="R4" t="n">
-        <v>6850297</v>
+        <v>6850260</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Med apothecier.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129669938</v>
+        <v>129669806</v>
       </c>
       <c r="B5" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498751</v>
+        <v>498780</v>
       </c>
       <c r="R5" t="n">
-        <v>6850235</v>
+        <v>6850297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129669907</v>
+        <v>129669938</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>92925</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498744</v>
+        <v>498751</v>
       </c>
       <c r="R6" t="n">
-        <v>6850260</v>
+        <v>6850235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Med apothecier.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 47876-2025 artfynd.xlsx
+++ b/artfynd/A 47876-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129669963</v>
       </c>
       <c r="B2" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129669857</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129669907</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129669806</v>
       </c>
       <c r="B5" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129669938</v>
       </c>
       <c r="B6" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47876-2025 artfynd.xlsx
+++ b/artfynd/A 47876-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129669963</v>
+        <v>129669806</v>
       </c>
       <c r="B2" t="n">
-        <v>78845</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498775</v>
+        <v>498780</v>
       </c>
       <c r="R2" t="n">
-        <v>6850276</v>
+        <v>6850297</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129669857</v>
+        <v>129669938</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498762</v>
+        <v>498751</v>
       </c>
       <c r="R3" t="n">
-        <v>6850294</v>
+        <v>6850235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,14 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129669907</v>
+        <v>129669857</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498744</v>
+        <v>498762</v>
       </c>
       <c r="R4" t="n">
-        <v>6850260</v>
+        <v>6850294</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Med apothecier.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129669806</v>
+        <v>129669907</v>
       </c>
       <c r="B5" t="n">
-        <v>92926</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498780</v>
+        <v>498744</v>
       </c>
       <c r="R5" t="n">
-        <v>6850297</v>
+        <v>6850260</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Med apothecier.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129669938</v>
+        <v>129669664</v>
       </c>
       <c r="B6" t="n">
-        <v>92926</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498751</v>
+        <v>498737</v>
       </c>
       <c r="R6" t="n">
-        <v>6850235</v>
+        <v>6850227</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,6 +1162,200 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129669963</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nordkap, Nordkap, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>498775</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6850276</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129669674</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nordkap, Nordkap, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>498736</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6850226</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47876-2025 artfynd.xlsx
+++ b/artfynd/A 47876-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669806</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669938</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669857</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669907</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669664</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669963</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,8 +1391,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669674</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>